--- a/Layout Polizas/RENOVACION/TECMA (OLMES)/BASE EBPORTAL _ TECMA.xlsx
+++ b/Layout Polizas/RENOVACION/TECMA (OLMES)/BASE EBPORTAL _ TECMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://axa365-my.sharepoint.com/personal/emanuelesau_mejia_consultor_axa_com_mx/Documents/01.WinDevice/Desktop/Area de Trabajo/PoC-Emision-Proceso/PoC-Proceso-Emision/Layout Polizas/RENOVACION/TECMA (OLMES)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_AD4D2F04E46CFB4ACB3E2039BD55EC1C683EDF24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DDA4E4A-7CBD-48FA-A78A-2172124FB155}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_AD4D2F04E46CFB4ACB3E2039BD55EC1C683EDF24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A4710AD-D462-4720-A9D6-F77A6B10E106}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5223,6 +5223,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5491,6 +5495,7 @@
   <dimension ref="A1:AA1331"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.7109375" bestFit="1" customWidth="1"/>
